--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486481_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486481_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.673500000000001</v>
+        <v>7.5445</v>
       </c>
       <c r="E2" t="n">
-        <v>9.2798</v>
+        <v>7.1816</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3937</v>
+        <v>0.3629</v>
       </c>
       <c r="G2" t="n">
         <v>4.9548</v>
@@ -610,13 +610,13 @@
         <v>2.6101</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7612</v>
+        <v>1.6322</v>
       </c>
       <c r="T2" t="n">
-        <v>3.9909</v>
+        <v>1.8927</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2297</v>
+        <v>-0.2605</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5649999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5716</v>
+        <v>7.5264</v>
       </c>
       <c r="E3" t="n">
-        <v>6.7568</v>
+        <v>7.4959</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1853</v>
+        <v>0.0305</v>
       </c>
       <c r="G3" t="n">
         <v>3.4658</v>
@@ -688,13 +688,13 @@
         <v>2.6101</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0242</v>
+        <v>-0.0694</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.536</v>
+        <v>0.2031</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4883</v>
+        <v>-0.2725</v>
       </c>
       <c r="V3" t="n">
         <v>2.8249</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4801</v>
+        <v>2.4184</v>
       </c>
       <c r="E4" t="n">
         <v>2.5664</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0864</v>
+        <v>-0.148</v>
       </c>
       <c r="G4" t="n">
         <v>1.6632</v>
@@ -766,13 +766,13 @@
         <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8169</v>
+        <v>0.7553</v>
       </c>
       <c r="T4" t="n">
         <v>0.5516</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2653</v>
+        <v>0.2037</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>X. OROZ URIA</t>
+          <t>J. VRANKIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.525</v>
+        <v>1.5866</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0609</v>
+        <v>1.2054</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5359</v>
+        <v>0.3812</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1655</v>
+        <v>-0.77</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3687</v>
+        <v>3.0231</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2032</v>
+        <v>-3.793</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6158</v>
+        <v>0.8542</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3536</v>
+        <v>2.9929</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2622</v>
+        <v>-2.1387</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4504</v>
+        <v>-1.6241</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0151</v>
+        <v>0.0302</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4654</v>
+        <v>-1.6543</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1751</v>
+        <v>-1.305</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6525</v>
+        <v>2.6101</v>
       </c>
       <c r="S5" t="n">
-        <v>0.882</v>
+        <v>-0.0784</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6201</v>
+        <v>0.5264</v>
       </c>
       <c r="U5" t="n">
-        <v>0.262</v>
+        <v>-0.6048</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. VRANKIC</t>
+          <t>I. JAKOVICS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.413</v>
+        <v>0.6819</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0626</v>
+        <v>0.606</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3503</v>
+        <v>0.0759</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.77</v>
+        <v>1.9344</v>
       </c>
       <c r="H6" t="n">
-        <v>3.0231</v>
+        <v>0.6506</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.793</v>
+        <v>1.2838</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8542</v>
+        <v>3.6566</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9929</v>
+        <v>0.803</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.1387</v>
+        <v>2.8536</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6241</v>
+        <v>-1.7222</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0302</v>
+        <v>-0.1523</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.6543</v>
+        <v>-1.5698</v>
       </c>
       <c r="P6" t="n">
-        <v>1.305</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.305</v>
+        <v>-3.4801</v>
       </c>
       <c r="R6" t="n">
-        <v>2.6101</v>
+        <v>2.8276</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2521</v>
+        <v>-0.6</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6165</v>
+        <v>0.2343</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.8343</v>
       </c>
       <c r="V6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. JAKOVICS</t>
+          <t>V. VUCETIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1017</v>
+        <v>0.4809</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3133</v>
+        <v>3.7043</v>
       </c>
       <c r="F7" t="n">
-        <v>0.415</v>
+        <v>-3.2234</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9344</v>
+        <v>0.3167</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6506</v>
+        <v>0.9064</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2838</v>
+        <v>-0.5897</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6566</v>
+        <v>2.501</v>
       </c>
       <c r="K7" t="n">
-        <v>0.803</v>
+        <v>0.6268</v>
       </c>
       <c r="L7" t="n">
-        <v>2.8536</v>
+        <v>1.8742</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7222</v>
+        <v>-2.1843</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1523</v>
+        <v>0.2796</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5698</v>
+        <v>-2.4639</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.4801</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.8276</v>
+        <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1802</v>
+        <v>0.0544</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.0733</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4952</v>
+        <v>-0.0189</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.7602</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1952</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V. VUCETIC</t>
+          <t>X. OROZ URIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0701</v>
+        <v>0.1897</v>
       </c>
       <c r="E8" t="n">
-        <v>3.369</v>
+        <v>0.7256</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.4391</v>
+        <v>-0.5359</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3167</v>
+        <v>1.1655</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9064</v>
+        <v>1.3687</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5897</v>
+        <v>-0.2032</v>
       </c>
       <c r="J8" t="n">
-        <v>2.501</v>
+        <v>2.6158</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6268</v>
+        <v>1.3536</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8742</v>
+        <v>1.2622</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1843</v>
+        <v>-1.4504</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2796</v>
+        <v>0.0151</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.4639</v>
+        <v>-1.4654</v>
       </c>
       <c r="P8" t="n">
-        <v>0.87</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4967</v>
+        <v>0.5468</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.262</v>
+        <v>0.2848</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2347</v>
+        <v>0.262</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7602</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.8902</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9896</v>
+        <v>-0.7592</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2605</v>
+        <v>-0.9685</v>
       </c>
       <c r="F9" t="n">
-        <v>0.271</v>
+        <v>0.2093</v>
       </c>
       <c r="G9" t="n">
         <v>0.709</v>
@@ -1156,13 +1156,13 @@
         <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0839</v>
+        <v>0.3142</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.2235</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1524</v>
+        <v>0.0907</v>
       </c>
       <c r="V9" t="n">
         <v>-1.13</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. HERON</t>
+          <t>A. MUÑOZ BORCHERS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3271</v>
+        <v>-1.416</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5753</v>
+        <v>0.7436</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7518</v>
+        <v>-2.1596</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7318</v>
+        <v>-2.3474</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0735</v>
+        <v>1.4599</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6582</v>
+        <v>-3.8074</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6424</v>
+        <v>-1.1616</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.0886</v>
+        <v>1.6274</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5538</v>
+        <v>-2.789</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0893</v>
+        <v>-1.1858</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0151</v>
+        <v>-0.1674</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1044</v>
+        <v>-1.0184</v>
       </c>
       <c r="P10" t="n">
         <v>1.0875</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6423</v>
+        <v>0.4089</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2846</v>
+        <v>0.2103</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6423</v>
+        <v>0.1986</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.3252</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.695</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.3252</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MUÑOZ BORCHERS</t>
+          <t>M. HERON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5972</v>
+        <v>-1.5515</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4084</v>
+        <v>-0.9539</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0055</v>
+        <v>-0.5977</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.3474</v>
+        <v>-1.7318</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4599</v>
+        <v>-1.0735</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.8074</v>
+        <v>-0.6582</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1616</v>
+        <v>-1.6424</v>
       </c>
       <c r="K11" t="n">
-        <v>1.6274</v>
+        <v>-1.0886</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.789</v>
+        <v>-0.5538</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1858</v>
+        <v>-0.0893</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1674</v>
+        <v>0.0151</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0184</v>
+        <v>-0.1044</v>
       </c>
       <c r="P11" t="n">
         <v>1.0875</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2277</v>
+        <v>0.4179</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.125</v>
+        <v>0.9061</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3527</v>
+        <v>-0.4882</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.3252</v>
       </c>
       <c r="W11" t="n">
-        <v>1.695</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.2599</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6459</v>
+        <v>-5.8819</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6593</v>
+        <v>-3.926</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9866</v>
+        <v>-1.9558</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9129</v>
@@ -1390,13 +1390,13 @@
         <v>2.1751</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3991</v>
+        <v>0.1631</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0791</v>
+        <v>0.8124</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.68</v>
+        <v>-0.6492</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8695</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.13499999999999</v>
+        <v>10.8198</v>
       </c>
       <c r="E13" t="n">
-        <v>17.6955</v>
+        <v>18.3804</v>
       </c>
       <c r="F13" t="n">
         <v>-7.5606</v>
       </c>
       <c r="G13" t="n">
-        <v>8.447299999999998</v>
+        <v>8.4473</v>
       </c>
       <c r="H13" t="n">
         <v>13.0173</v>
@@ -1441,7 +1441,7 @@
         <v>-4.57</v>
       </c>
       <c r="J13" t="n">
-        <v>22.4972</v>
+        <v>22.49720000000001</v>
       </c>
       <c r="K13" t="n">
         <v>13.7036</v>
@@ -1468,10 +1468,10 @@
         <v>18.488</v>
       </c>
       <c r="S13" t="n">
-        <v>2.859900000000001</v>
+        <v>3.545</v>
       </c>
       <c r="T13" t="n">
-        <v>5.2333</v>
+        <v>5.918500000000001</v>
       </c>
       <c r="U13" t="n">
         <v>-2.3734</v>
@@ -1480,7 +1480,7 @@
         <v>-2.26</v>
       </c>
       <c r="W13" t="n">
-        <v>7.365499999999999</v>
+        <v>7.3655</v>
       </c>
       <c r="X13" t="n">
         <v>-9.625399999999999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. JOU COLL</t>
+          <t>C. DE SOUZA PACHECO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3956</v>
+        <v>3.2195</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1162</v>
+        <v>4.3481</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2794</v>
+        <v>-1.1286</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6087</v>
+        <v>2.5397</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.424</v>
+        <v>0.9794</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8153</v>
+        <v>1.5602</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1071</v>
+        <v>4.9544</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.3441</v>
+        <v>2.5247</v>
       </c>
       <c r="L14" t="n">
-        <v>2.4512</v>
+        <v>2.4296</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.7158</v>
+        <v>-2.4147</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0799</v>
+        <v>-1.5453</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6359</v>
+        <v>-0.8694</v>
       </c>
       <c r="P14" t="n">
-        <v>2.6101</v>
+        <v>-0.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R14" t="n">
-        <v>2.6101</v>
+        <v>1.305</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0038</v>
+        <v>-0.1451</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6187</v>
+        <v>-0.1262</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6149</v>
+        <v>-0.0189</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3904</v>
+        <v>1.695</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3904</v>
+        <v>1.695</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. DE SOUZA PACHECO</t>
+          <t>G. JOU COLL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2959</v>
+        <v>2.7058</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7893</v>
+        <v>2.3339</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4934</v>
+        <v>0.3719</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5397</v>
+        <v>-0.6087</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9794</v>
+        <v>-2.424</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5602</v>
+        <v>1.8153</v>
       </c>
       <c r="J15" t="n">
-        <v>4.9544</v>
+        <v>1.1071</v>
       </c>
       <c r="K15" t="n">
-        <v>2.5247</v>
+        <v>-1.3441</v>
       </c>
       <c r="L15" t="n">
-        <v>2.4296</v>
+        <v>2.4512</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.4147</v>
+        <v>-1.7158</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5453</v>
+        <v>-1.0799</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8694</v>
+        <v>-0.6359</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.87</v>
+        <v>2.6101</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.305</v>
+        <v>2.6101</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0687</v>
+        <v>0.3139</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.8364</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3837</v>
+        <v>-0.5224</v>
       </c>
       <c r="V15" t="n">
-        <v>1.695</v>
+        <v>0.3904</v>
       </c>
       <c r="W15" t="n">
-        <v>1.695</v>
+        <v>0.3904</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7747</v>
+        <v>1.0849</v>
       </c>
       <c r="E16" t="n">
-        <v>1.212</v>
+        <v>0.4297</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5627</v>
+        <v>0.6552</v>
       </c>
       <c r="G16" t="n">
         <v>-0.1436</v>
@@ -1702,13 +1702,13 @@
         <v>0.6525</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2658</v>
+        <v>0.5759</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3531</v>
+        <v>0.5708</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.08740000000000001</v>
+        <v>0.0051</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2363</v>
+        <v>-0.1491</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2374</v>
+        <v>2.7903</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.0011</v>
+        <v>-2.9395</v>
       </c>
       <c r="G17" t="n">
         <v>1.0716</v>
@@ -1780,13 +1780,13 @@
         <v>2.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2947</v>
+        <v>-0.0907</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0791</v>
+        <v>0.6321</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7845</v>
+        <v>-0.7228</v>
       </c>
       <c r="V17" t="n">
         <v>-1.13</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. DIAZ ALEJANO</t>
+          <t>S. BARRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1203</v>
+        <v>-0.1772</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2291</v>
+        <v>2.4198</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1087</v>
+        <v>-2.597</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2974</v>
+        <v>-0.6394</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1276</v>
+        <v>-0.1947</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1698</v>
+        <v>-0.4447</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1646</v>
+        <v>0.7935</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4234</v>
+        <v>0.6022</v>
       </c>
       <c r="L18" t="n">
-        <v>1.7412</v>
+        <v>0.1912</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8672</v>
+        <v>-1.4328</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2959</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5714</v>
+        <v>-0.6359</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.3926</v>
+        <v>1.0875</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0856</v>
+        <v>-0.0604</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1971</v>
+        <v>0.4963</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1115</v>
+        <v>-0.5567</v>
       </c>
       <c r="V18" t="n">
-        <v>1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W18" t="n">
         <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. BARRO</t>
+          <t>J. DIAZ ALEJANO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.027</v>
+        <v>-0.3125</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5315</v>
+        <v>0.8938</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5045</v>
+        <v>-1.2063</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6394</v>
+        <v>1.2974</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1947</v>
+        <v>0.1276</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4447</v>
+        <v>1.1698</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7935</v>
+        <v>3.1646</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6022</v>
+        <v>1.4234</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1912</v>
+        <v>1.7412</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4328</v>
+        <v>-1.8672</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7969000000000001</v>
+        <v>-1.2959</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6359</v>
+        <v>-0.5714</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0875</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1438</v>
+        <v>-0.3473</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6081</v>
+        <v>-0.1382</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4642</v>
+        <v>-0.2091</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5649999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="W19" t="n">
         <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8223</v>
+        <v>-0.573</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1817</v>
+        <v>0.0418</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6405999999999999</v>
+        <v>-0.6148</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6235000000000001</v>
@@ -2014,13 +2014,13 @@
         <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6338</v>
+        <v>-0.3845</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.411</v>
+        <v>-0.1875</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2228</v>
+        <v>-0.1971</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5915</v>
+        <v>-1.3565</v>
       </c>
       <c r="E21" t="n">
-        <v>0.821</v>
+        <v>0.9327</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4125</v>
+        <v>-2.2892</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9044</v>
@@ -2092,13 +2092,13 @@
         <v>2.1751</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9248</v>
+        <v>-0.6898</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2656</v>
+        <v>0.3773</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1904</v>
+        <v>-1.0671</v>
       </c>
       <c r="V21" t="n">
         <v>1.3252</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8758</v>
+        <v>-2.2875</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1189</v>
+        <v>-1.8954</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7569</v>
+        <v>-0.3921</v>
       </c>
       <c r="G22" t="n">
         <v>0.5528999999999999</v>
@@ -2170,13 +2170,13 @@
         <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6457000000000001</v>
+        <v>-0.0574</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.411</v>
+        <v>-0.1875</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2347</v>
+        <v>0.1301</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3904</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0182</v>
+        <v>-2.8486</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.581</v>
+        <v>-1.134</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4371</v>
+        <v>-1.7146</v>
       </c>
       <c r="G23" t="n">
         <v>-3.4992</v>
@@ -2248,13 +2248,13 @@
         <v>2.6101</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.519</v>
+        <v>-0.3494</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0601</v>
+        <v>0.5071</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.8565</v>
       </c>
       <c r="V23" t="n">
         <v>0.5649999999999999</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0881</v>
+        <v>-3.7271</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3557</v>
+        <v>-2.0204</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7325</v>
+        <v>-1.7067</v>
       </c>
       <c r="G24" t="n">
         <v>-4.1119</v>
@@ -2326,13 +2326,13 @@
         <v>1.0875</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5412</v>
+        <v>-0.1803</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6165</v>
+        <v>-0.2812</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0752</v>
+        <v>0.1009</v>
       </c>
       <c r="V24" t="n">
         <v>0.5649999999999999</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5889</v>
+        <v>-4.9685</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.1386</v>
+        <v>-1.5798</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.4504</v>
+        <v>-3.3887</v>
       </c>
       <c r="G25" t="n">
         <v>-3.3783</v>
@@ -2404,13 +2404,13 @@
         <v>1.5225</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3204</v>
+        <v>-0.7</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.1262</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6355</v>
+        <v>-0.5738</v>
       </c>
       <c r="V25" t="n">
         <v>-1.3252</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-10.135</v>
+        <v>-9.389799999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>7.560600000000001</v>
+        <v>7.560499999999998</v>
       </c>
       <c r="F26" t="n">
-        <v>-17.6956</v>
+        <v>-16.9504</v>
       </c>
       <c r="G26" t="n">
         <v>-8.4474</v>
@@ -2482,13 +2482,13 @@
         <v>17.4004</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.8599</v>
+        <v>-2.1151</v>
       </c>
       <c r="T26" t="n">
-        <v>2.373299999999999</v>
+        <v>2.3732</v>
       </c>
       <c r="U26" t="n">
-        <v>-5.233499999999999</v>
+        <v>-4.4883</v>
       </c>
       <c r="V26" t="n">
         <v>2.26</v>
